--- a/[tobe]Estimation.xlsx
+++ b/[tobe]Estimation.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="99">
   <si>
     <t>Development Effort &amp; Cost Estimation (MD &amp; USD)</t>
   </si>
@@ -41,135 +41,135 @@
     <t>Monthly Cost (USD)</t>
   </si>
   <si>
+    <t>3-Month Estimate (USD)</t>
+  </si>
+  <si>
     <t>1.1 Project Setup &amp; Cloud Infrastructure</t>
   </si>
   <si>
-    <t>3-Month Estimate (USD)</t>
-  </si>
-  <si>
     <t>Development Phase (3 months)</t>
   </si>
   <si>
     <t>Azure AI Search</t>
   </si>
   <si>
+    <t>Architecture &amp; tech stack finalization</t>
+  </si>
+  <si>
+    <t>Azure resource provisioning (Entra ID, Blob, AI Search, OpenAI, PostgreSQL, Redis, VNet)</t>
+  </si>
+  <si>
+    <t>CI/CD pipeline (GitHub Actions / Azure DevOps)</t>
+  </si>
+  <si>
     <t>Azure OpenAI (development/testing quota)</t>
   </si>
   <si>
-    <t>Architecture &amp; tech stack finalization</t>
+    <t>Monitoring &amp; logging setup (App Insights, alerts)</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
   </si>
   <si>
     <t>Azure Database for PostgreSQL</t>
   </si>
   <si>
-    <t>Azure resource provisioning (Entra ID, Blob, AI Search, OpenAI, PostgreSQL, Redis, VNet)</t>
-  </si>
-  <si>
     <t>Azure Blob Storage + Files</t>
   </si>
   <si>
-    <t>CI/CD pipeline (GitHub Actions / Azure DevOps)</t>
-  </si>
-  <si>
-    <t>Monitoring &amp; logging setup (App Insights, alerts)</t>
+    <t>1.2 Authentication &amp; Authorization (FR-1)</t>
+  </si>
+  <si>
+    <t>Azure Entra ID app registration &amp; OAuth2/OIDC configuration</t>
   </si>
   <si>
     <t>Azure Cache for Redis</t>
   </si>
   <si>
-    <t>Subtotal</t>
+    <t>Backend JWT validation &amp; FastAPI auth middleware</t>
   </si>
   <si>
     <t>Azure Monitor / App Insights / Log Analytics</t>
   </si>
   <si>
-    <t>1.2 Authentication &amp; Authorization (FR-1)</t>
+    <t>RBAC (Vendor / Customer role enforcement)</t>
   </si>
   <si>
     <t>Key Vault, VNet, private networking &amp; DNS</t>
   </si>
   <si>
-    <t>Azure Entra ID app registration &amp; OAuth2/OIDC configuration</t>
+    <t>Login/logout UI (React)</t>
   </si>
   <si>
     <t>CI/CD, test runner, and support tooling</t>
   </si>
   <si>
-    <t>Backend JWT validation &amp; FastAPI auth middleware</t>
-  </si>
-  <si>
     <t>Estimated Total (Development)</t>
   </si>
   <si>
-    <t>RBAC (Vendor / Customer role enforcement)</t>
+    <t>1.3 Frontend Application (React SPA)</t>
+  </si>
+  <si>
+    <t>Project scaffolding, routing, shared components</t>
   </si>
   <si>
     <t>Production Phase (steady state)</t>
   </si>
   <si>
-    <t>Login/logout UI (React)</t>
+    <t>Document submission &amp; checklist UI</t>
+  </si>
+  <si>
+    <t>Audit report viewing &amp; evidence browsing UI</t>
+  </si>
+  <si>
+    <t>Accept/reject decision workflow UI</t>
   </si>
   <si>
     <t>Azure AI Search (standard tier, indexing + queries)</t>
   </si>
   <si>
+    <t>Natural language search / Q&amp;A interface</t>
+  </si>
+  <si>
     <t>Azure OpenAI (production inference + embeddings)</t>
   </si>
   <si>
-    <t>1.3 Frontend Application (React SPA)</t>
-  </si>
-  <si>
-    <t>Project scaffolding, routing, shared components</t>
-  </si>
-  <si>
-    <t>Document submission &amp; checklist UI</t>
-  </si>
-  <si>
-    <t>Audit report viewing &amp; evidence browsing UI</t>
-  </si>
-  <si>
-    <t>Accept/reject decision workflow UI</t>
-  </si>
-  <si>
-    <t>Natural language search / Q&amp;A interface</t>
-  </si>
-  <si>
     <t>Audit template management UI</t>
   </si>
   <si>
     <t>Document source addition UI</t>
   </si>
   <si>
+    <t>Expert identification UI</t>
+  </si>
+  <si>
+    <t>Responsive design &amp; cross-browser polish (Chrome/Edge 130+)</t>
+  </si>
+  <si>
+    <t>1.4 Backend API (Python / FastAPI)</t>
+  </si>
+  <si>
     <t>Alerting, autoscale support, and operational overhead</t>
   </si>
   <si>
-    <t>Expert identification UI</t>
+    <t>Project scaffolding, DB models (PostgreSQL), migrations</t>
+  </si>
+  <si>
+    <t>Document upload &amp; submission API (incl. Blob Storage)</t>
   </si>
   <si>
     <t>Estimated Total (Production)</t>
   </si>
   <si>
-    <t>Responsive design &amp; cross-browser polish (Chrome/Edge 130+)</t>
+    <t>Audit template CRUD API</t>
+  </si>
+  <si>
+    <t>Audit report &amp; review decision API</t>
   </si>
   <si>
     <t>Note: Production monthly cost (~$3,920) is below the $5,000/month operating cap.</t>
   </si>
   <si>
-    <t>1.4 Backend API (Python / FastAPI)</t>
-  </si>
-  <si>
-    <t>Project scaffolding, DB models (PostgreSQL), migrations</t>
-  </si>
-  <si>
-    <t>Document upload &amp; submission API (incl. Blob Storage)</t>
-  </si>
-  <si>
-    <t>Audit template CRUD API</t>
-  </si>
-  <si>
-    <t>Audit report &amp; review decision API</t>
-  </si>
-  <si>
     <t>Search query API (NL → AI Search → OpenAI)</t>
   </si>
   <si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>Stakeholder training &amp; handover</t>
+  </si>
+  <si>
+    <t>1.12 Risk Buffers</t>
   </si>
   <si>
     <t>Azure service integration delays (quota limits, API changes)</t>
@@ -438,7 +441,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -459,11 +462,11 @@
     <xf borderId="3" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -472,13 +475,16 @@
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="1" fillId="4" fontId="8" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="2" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -737,45 +743,45 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="7"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="11">
+        <v>13</v>
+      </c>
+      <c r="B7" s="10">
         <v>4.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="11">
+        <v>14</v>
+      </c>
+      <c r="B8" s="10">
         <v>6.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="11">
+        <v>15</v>
+      </c>
+      <c r="B9" s="10">
         <v>4.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="11">
+        <v>17</v>
+      </c>
+      <c r="B10" s="10">
         <v>2.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B11" s="13">
         <v>16.0</v>
@@ -783,13 +789,13 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" s="7"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B13" s="14">
         <v>2.0</v>
@@ -797,7 +803,7 @@
     </row>
     <row r="14">
       <c r="A14" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B14" s="14">
         <v>2.0</v>
@@ -805,7 +811,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B15" s="14">
         <v>2.0</v>
@@ -813,7 +819,7 @@
     </row>
     <row r="16">
       <c r="A16" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B16" s="14">
         <v>2.0</v>
@@ -821,55 +827,55 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="16">
+        <v>18</v>
+      </c>
+      <c r="B17" s="15">
         <v>8.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B18" s="7"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="11">
+        <v>32</v>
+      </c>
+      <c r="B19" s="10">
         <v>6.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="11">
+        <v>34</v>
+      </c>
+      <c r="B20" s="10">
         <v>8.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="11">
+        <v>35</v>
+      </c>
+      <c r="B21" s="10">
         <v>8.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="11">
+        <v>36</v>
+      </c>
+      <c r="B22" s="10">
         <v>6.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="11">
+        <v>38</v>
+      </c>
+      <c r="B23" s="10">
         <v>10.0</v>
       </c>
     </row>
@@ -877,7 +883,7 @@
       <c r="A24" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="10">
         <v>6.0</v>
       </c>
     </row>
@@ -885,29 +891,29 @@
       <c r="A25" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>4.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="11">
+        <v>42</v>
+      </c>
+      <c r="B26" s="10">
         <v>4.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="11">
+        <v>43</v>
+      </c>
+      <c r="B27" s="10">
         <v>4.0</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B28" s="13">
         <v>56.0</v>
@@ -915,39 +921,39 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B29" s="7"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="11">
+        <v>46</v>
+      </c>
+      <c r="B30" s="10">
         <v>6.0</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31" s="11">
+        <v>47</v>
+      </c>
+      <c r="B31" s="10">
         <v>6.0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="11">
+        <v>49</v>
+      </c>
+      <c r="B32" s="10">
         <v>4.0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="11">
+        <v>50</v>
+      </c>
+      <c r="B33" s="10">
         <v>6.0</v>
       </c>
     </row>
@@ -955,7 +961,7 @@
       <c r="A34" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="10">
         <v>8.0</v>
       </c>
     </row>
@@ -963,7 +969,7 @@
       <c r="A35" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="10">
         <v>4.0</v>
       </c>
     </row>
@@ -971,7 +977,7 @@
       <c r="A36" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="10">
         <v>8.0</v>
       </c>
     </row>
@@ -979,13 +985,13 @@
       <c r="A37" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="10">
         <v>4.0</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B38" s="13">
         <v>46.0</v>
@@ -1001,7 +1007,7 @@
       <c r="A40" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="10">
         <v>6.0</v>
       </c>
     </row>
@@ -1009,7 +1015,7 @@
       <c r="A41" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="11">
+      <c r="B41" s="10">
         <v>10.0</v>
       </c>
     </row>
@@ -1017,7 +1023,7 @@
       <c r="A42" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="11">
+      <c r="B42" s="10">
         <v>10.0</v>
       </c>
     </row>
@@ -1025,7 +1031,7 @@
       <c r="A43" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B43" s="11">
+      <c r="B43" s="10">
         <v>4.0</v>
       </c>
     </row>
@@ -1033,13 +1039,13 @@
       <c r="A44" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B44" s="11">
+      <c r="B44" s="10">
         <v>4.0</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B45" s="13">
         <v>34.0</v>
@@ -1055,7 +1061,7 @@
       <c r="A47" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="10">
         <v>4.0</v>
       </c>
     </row>
@@ -1063,7 +1069,7 @@
       <c r="A48" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="10">
         <v>4.0</v>
       </c>
     </row>
@@ -1071,7 +1077,7 @@
       <c r="A49" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="10">
         <v>6.0</v>
       </c>
     </row>
@@ -1079,7 +1085,7 @@
       <c r="A50" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="11">
+      <c r="B50" s="10">
         <v>6.0</v>
       </c>
     </row>
@@ -1087,7 +1093,7 @@
       <c r="A51" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B51" s="11">
+      <c r="B51" s="10">
         <v>4.0</v>
       </c>
     </row>
@@ -1095,13 +1101,13 @@
       <c r="A52" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B52" s="11">
+      <c r="B52" s="10">
         <v>2.0</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B53" s="13">
         <v>26.0</v>
@@ -1117,7 +1123,7 @@
       <c r="A55" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B55" s="11">
+      <c r="B55" s="10">
         <v>4.0</v>
       </c>
     </row>
@@ -1125,7 +1131,7 @@
       <c r="A56" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B56" s="11">
+      <c r="B56" s="10">
         <v>2.0</v>
       </c>
     </row>
@@ -1133,13 +1139,13 @@
       <c r="A57" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B57" s="11">
+      <c r="B57" s="10">
         <v>4.0</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B58" s="13">
         <v>10.0</v>
@@ -1155,7 +1161,7 @@
       <c r="A60" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B60" s="11">
+      <c r="B60" s="10">
         <v>4.0</v>
       </c>
     </row>
@@ -1163,7 +1169,7 @@
       <c r="A61" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="11">
+      <c r="B61" s="10">
         <v>2.0</v>
       </c>
     </row>
@@ -1171,13 +1177,13 @@
       <c r="A62" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B62" s="11">
+      <c r="B62" s="10">
         <v>4.0</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B63" s="13">
         <v>10.0</v>
@@ -1193,7 +1199,7 @@
       <c r="A65" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B65" s="11">
+      <c r="B65" s="10">
         <v>6.0</v>
       </c>
     </row>
@@ -1201,7 +1207,7 @@
       <c r="A66" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B66" s="11">
+      <c r="B66" s="10">
         <v>6.0</v>
       </c>
     </row>
@@ -1209,7 +1215,7 @@
       <c r="A67" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B67" s="11">
+      <c r="B67" s="10">
         <v>6.0</v>
       </c>
     </row>
@@ -1217,13 +1223,13 @@
       <c r="A68" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B68" s="11">
+      <c r="B68" s="10">
         <v>8.0</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B69" s="13">
         <v>26.0</v>
@@ -1277,9 +1283,9 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B76" s="16">
+        <v>18</v>
+      </c>
+      <c r="B76" s="15">
         <v>14.0</v>
       </c>
     </row>
@@ -1293,7 +1299,7 @@
       <c r="A78" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B78" s="11">
+      <c r="B78" s="10">
         <v>6.0</v>
       </c>
     </row>
@@ -1301,7 +1307,7 @@
       <c r="A79" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B79" s="11">
+      <c r="B79" s="10">
         <v>4.0</v>
       </c>
     </row>
@@ -1309,7 +1315,7 @@
       <c r="A80" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B80" s="11">
+      <c r="B80" s="10">
         <v>4.0</v>
       </c>
     </row>
@@ -1317,51 +1323,51 @@
       <c r="A81" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B81" s="11">
+      <c r="B81" s="10">
         <v>4.0</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B82" s="13">
         <v>18.0</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="6" t="s">
-        <v>88</v>
+      <c r="A83" s="18" t="s">
+        <v>93</v>
       </c>
       <c r="B83" s="7"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="B84" s="11">
+      <c r="A84" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B84" s="10">
         <v>10.0</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B85" s="11">
+        <v>95</v>
+      </c>
+      <c r="B85" s="10">
         <v>10.0</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B86" s="11">
+        <v>96</v>
+      </c>
+      <c r="B86" s="10">
         <v>8.0</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B87" s="13">
         <v>28.0</v>
@@ -1369,15 +1375,15 @@
     </row>
     <row r="88" ht="15.75" customHeight="1"/>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="19" t="s">
-        <v>96</v>
+      <c r="A89" s="20" t="s">
+        <v>97</v>
       </c>
       <c r="B89" s="7"/>
     </row>
     <row r="90" ht="15.75" customHeight="1"/>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="19" t="s">
-        <v>97</v>
+      <c r="A91" s="20" t="s">
+        <v>98</v>
       </c>
       <c r="B91" s="7"/>
     </row>
@@ -2301,8 +2307,8 @@
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="A70:B70"/>
     <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A83:B83"/>
     <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A83:B83"/>
     <mergeCell ref="A91:B91"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A12:B12"/>
@@ -2355,7 +2361,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -2369,104 +2375,104 @@
       <c r="A7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="11">
         <v>120.0</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="11">
         <v>360.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="10">
+        <v>16</v>
+      </c>
+      <c r="B8" s="11">
         <v>900.0</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="11">
         <v>2700.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="10">
+        <v>19</v>
+      </c>
+      <c r="B9" s="11">
         <v>150.0</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="11">
         <v>450.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="10">
+        <v>20</v>
+      </c>
+      <c r="B10" s="11">
         <v>35.0</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="11">
         <v>105.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="10">
+        <v>23</v>
+      </c>
+      <c r="B11" s="11">
         <v>70.0</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="11">
         <v>210.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="10">
+        <v>25</v>
+      </c>
+      <c r="B12" s="11">
         <v>90.0</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="11">
         <v>270.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="10">
+        <v>27</v>
+      </c>
+      <c r="B13" s="11">
         <v>60.0</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="11">
         <v>180.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="10">
+        <v>29</v>
+      </c>
+      <c r="B14" s="11">
         <v>80.0</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="11">
         <v>240.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="15">
+        <v>30</v>
+      </c>
+      <c r="B15" s="16">
         <v>1505.0</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="16">
         <v>4515.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="7"/>
@@ -2482,81 +2488,81 @@
     </row>
     <row r="19">
       <c r="A19" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="10">
+        <v>37</v>
+      </c>
+      <c r="B19" s="11">
         <v>350.0</v>
       </c>
       <c r="C19" s="9"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="10">
+        <v>39</v>
+      </c>
+      <c r="B20" s="11">
         <v>2500.0</v>
       </c>
       <c r="C20" s="9"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="10">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11">
         <v>350.0</v>
       </c>
       <c r="C21" s="9"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="10">
+        <v>20</v>
+      </c>
+      <c r="B22" s="11">
         <v>120.0</v>
       </c>
       <c r="C22" s="9"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="10">
+        <v>23</v>
+      </c>
+      <c r="B23" s="11">
         <v>150.0</v>
       </c>
       <c r="C23" s="9"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="10">
+        <v>25</v>
+      </c>
+      <c r="B24" s="11">
         <v>200.0</v>
       </c>
       <c r="C24" s="9"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="10">
+        <v>27</v>
+      </c>
+      <c r="B25" s="11">
         <v>150.0</v>
       </c>
       <c r="C25" s="9"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="10">
+        <v>45</v>
+      </c>
+      <c r="B26" s="11">
         <v>100.0</v>
       </c>
       <c r="C26" s="9"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="15">
+        <v>48</v>
+      </c>
+      <c r="B27" s="16">
         <v>3920.0</v>
       </c>
       <c r="C27" s="9"/>
@@ -2564,7 +2570,7 @@
     <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="17" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>
